--- a/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
@@ -565,10 +565,10 @@
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>10.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="12">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>56.82</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>65.19</v>
+        <v>61.59</v>
       </c>
       <c r="H25" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>65.84</v>
+        <v>62.21</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
@@ -539,10 +539,10 @@
         <v>4.6</v>
       </c>
       <c r="G10" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>43.7</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -591,10 +591,10 @@
         <v>0.1</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="13">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>53.22</v>
+        <v>81.22</v>
       </c>
     </row>
     <row r="15">
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>61.59</v>
+        <v>89.59</v>
       </c>
       <c r="H25" t="n">
-        <v>0.62</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>62.21</v>
+        <v>90.48999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 15 Herrería, carpintería y vidrios</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Barandas y pasamanos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
@@ -758,7 +758,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MO-OF1-SOLD</t>
+          <t>MO-OF1-PISOD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">

--- a/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-15-07-020.xlsx
@@ -758,7 +758,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MO-OF1-PISOD</t>
+          <t>MO-OF1-SOLD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
